--- a/AAII_Financials/Yearly/GORO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GORO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>GORO</t>
   </si>
@@ -732,25 +732,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>99800</v>
+        <v>23000</v>
       </c>
       <c r="E8" s="3">
-        <v>65700</v>
+        <v>20400</v>
       </c>
       <c r="F8" s="3">
-        <v>97700</v>
+        <v>9800</v>
       </c>
       <c r="G8" s="3">
-        <v>138700</v>
+        <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>125200</v>
+        <v>18400</v>
       </c>
       <c r="I8" s="3">
-        <v>90700</v>
+        <v>19900</v>
       </c>
       <c r="J8" s="3">
-        <v>120300</v>
+        <v>19400</v>
       </c>
       <c r="K8" s="3">
         <v>115300</v>
@@ -783,25 +783,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>61800</v>
+        <v>17000</v>
       </c>
       <c r="E9" s="3">
-        <v>68100</v>
+        <v>17400</v>
       </c>
       <c r="F9" s="3">
-        <v>76800</v>
+        <v>7800</v>
       </c>
       <c r="G9" s="3">
-        <v>81800</v>
+        <v>1000</v>
       </c>
       <c r="H9" s="3">
-        <v>72500</v>
+        <v>16200</v>
       </c>
       <c r="I9" s="3">
-        <v>60600</v>
+        <v>16800</v>
       </c>
       <c r="J9" s="3">
-        <v>73000</v>
+        <v>16000</v>
       </c>
       <c r="K9" s="3">
         <v>67100</v>
@@ -834,25 +834,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>38000</v>
+        <v>6000</v>
       </c>
       <c r="E10" s="3">
-        <v>-2400</v>
+        <v>2900</v>
       </c>
       <c r="F10" s="3">
-        <v>20900</v>
+        <v>2000</v>
       </c>
       <c r="G10" s="3">
-        <v>57000</v>
+        <v>-400</v>
       </c>
       <c r="H10" s="3">
-        <v>52700</v>
+        <v>2200</v>
       </c>
       <c r="I10" s="3">
-        <v>30000</v>
+        <v>3100</v>
       </c>
       <c r="J10" s="3">
-        <v>47300</v>
+        <v>3300</v>
       </c>
       <c r="K10" s="3">
         <v>48200</v>
@@ -1007,26 +1007,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3700</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>2400</v>
+        <v>-300</v>
       </c>
       <c r="I14" s="3">
-        <v>1300</v>
+        <v>-1200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="K14" s="3">
         <v>1900</v>
@@ -1059,25 +1059,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>11200</v>
+        <v>31900</v>
       </c>
       <c r="E15" s="3">
-        <v>18100</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <v>26100</v>
+        <v>5600</v>
       </c>
       <c r="G15" s="3">
-        <v>27200</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>16000</v>
+        <v>1700</v>
       </c>
       <c r="I15" s="3">
-        <v>17400</v>
+        <v>2100</v>
       </c>
       <c r="J15" s="3">
-        <v>19500</v>
+        <v>5100</v>
       </c>
       <c r="K15" s="3">
         <v>14600</v>
@@ -1128,25 +1128,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>82800</v>
+        <v>54000</v>
       </c>
       <c r="E17" s="3">
-        <v>93600</v>
+        <v>21700</v>
       </c>
       <c r="F17" s="3">
-        <v>117100</v>
+        <v>16800</v>
       </c>
       <c r="G17" s="3">
-        <v>132200</v>
+        <v>4300</v>
       </c>
       <c r="H17" s="3">
-        <v>103200</v>
+        <v>21000</v>
       </c>
       <c r="I17" s="3">
-        <v>90000</v>
+        <v>21900</v>
       </c>
       <c r="J17" s="3">
-        <v>104600</v>
+        <v>23700</v>
       </c>
       <c r="K17" s="3">
         <v>93400</v>
@@ -1179,25 +1179,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>17000</v>
+        <v>-31000</v>
       </c>
       <c r="E18" s="3">
-        <v>-27800</v>
+        <v>-1300</v>
       </c>
       <c r="F18" s="3">
-        <v>-19400</v>
+        <v>-7000</v>
       </c>
       <c r="G18" s="3">
-        <v>6500</v>
+        <v>-3800</v>
       </c>
       <c r="H18" s="3">
-        <v>22000</v>
+        <v>-2600</v>
       </c>
       <c r="I18" s="3">
-        <v>600</v>
+        <v>-2000</v>
       </c>
       <c r="J18" s="3">
-        <v>15700</v>
+        <v>-4400</v>
       </c>
       <c r="K18" s="3">
         <v>21900</v>
@@ -1251,25 +1251,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2400</v>
+        <v>37300</v>
       </c>
       <c r="E20" s="3">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
-        <v>2400</v>
+        <v>-1000</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>-700</v>
       </c>
       <c r="K20" s="3">
         <v>900</v>
@@ -1302,25 +1302,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>25800</v>
+        <v>-36500</v>
       </c>
       <c r="E21" s="3">
-        <v>-12200</v>
+        <v>-1300</v>
       </c>
       <c r="F21" s="3">
-        <v>6100</v>
+        <v>-900</v>
       </c>
       <c r="G21" s="3">
-        <v>31400</v>
+        <v>-2700</v>
       </c>
       <c r="H21" s="3">
-        <v>36100</v>
+        <v>800</v>
       </c>
       <c r="I21" s="3">
-        <v>18000</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
-        <v>35100</v>
+        <v>1400</v>
       </c>
       <c r="K21" s="3">
         <v>35600</v>
@@ -1353,25 +1353,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>10000</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>900</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>10</v>
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>300</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>10</v>
@@ -1404,25 +1404,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-47200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-30000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2200</v>
-      </c>
       <c r="H23" s="3">
-        <v>17600</v>
+        <v>-800</v>
       </c>
       <c r="I23" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J23" s="3">
-        <v>15500</v>
+        <v>-3400</v>
       </c>
       <c r="K23" s="3">
         <v>19000</v>
@@ -1454,26 +1454,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>3400</v>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E24" s="3">
-        <v>9300</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>8600</v>
+        <v>100</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H24" s="3">
-        <v>9600</v>
+        <v>200</v>
       </c>
       <c r="I24" s="3">
-        <v>5600</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="K24" s="3">
         <v>7200</v>
@@ -1557,25 +1557,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6500</v>
+        <v>-68400</v>
       </c>
       <c r="E26" s="3">
-        <v>-56500</v>
+        <v>-2500</v>
       </c>
       <c r="F26" s="3">
-        <v>-24100</v>
+        <v>-6700</v>
       </c>
       <c r="G26" s="3">
-        <v>-6300</v>
+        <v>-3100</v>
       </c>
       <c r="H26" s="3">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="I26" s="3">
-        <v>-6300</v>
+        <v>-1200</v>
       </c>
       <c r="J26" s="3">
-        <v>5500</v>
+        <v>-3900</v>
       </c>
       <c r="K26" s="3">
         <v>11900</v>
@@ -1608,25 +1608,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6500</v>
+        <v>-68400</v>
       </c>
       <c r="E27" s="3">
-        <v>-56500</v>
+        <v>-2500</v>
       </c>
       <c r="F27" s="3">
-        <v>-24100</v>
+        <v>-6800</v>
       </c>
       <c r="G27" s="3">
-        <v>-6300</v>
+        <v>-3000</v>
       </c>
       <c r="H27" s="3">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="I27" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="J27" s="3">
-        <v>5800</v>
+        <v>-3900</v>
       </c>
       <c r="K27" s="3">
         <v>9300</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>10700</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-2600</v>
@@ -1863,25 +1863,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2400</v>
+        <v>-37300</v>
       </c>
       <c r="E32" s="3">
-        <v>-2500</v>
+        <v>-1000</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
-        <v>-2400</v>
+        <v>1000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>1600</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>700</v>
       </c>
       <c r="K32" s="3">
         <v>-900</v>
@@ -1914,25 +1914,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6500</v>
+        <v>-68400</v>
       </c>
       <c r="E33" s="3">
-        <v>-56500</v>
+        <v>-2500</v>
       </c>
       <c r="F33" s="3">
-        <v>-24100</v>
+        <v>-6700</v>
       </c>
       <c r="G33" s="3">
-        <v>-6300</v>
+        <v>-3100</v>
       </c>
       <c r="H33" s="3">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="I33" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="J33" s="3">
-        <v>5800</v>
+        <v>-3900</v>
       </c>
       <c r="K33" s="3">
         <v>9300</v>
@@ -2016,25 +2016,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6500</v>
+        <v>-68400</v>
       </c>
       <c r="E35" s="3">
-        <v>-56500</v>
+        <v>-2500</v>
       </c>
       <c r="F35" s="3">
-        <v>-24100</v>
+        <v>-6700</v>
       </c>
       <c r="G35" s="3">
-        <v>-6300</v>
+        <v>-3100</v>
       </c>
       <c r="H35" s="3">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="I35" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="J35" s="3">
-        <v>5800</v>
+        <v>-3900</v>
       </c>
       <c r="K35" s="3">
         <v>9300</v>
@@ -2165,25 +2165,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>25000</v>
+        <v>9600</v>
       </c>
       <c r="E41" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="F41" s="3">
-        <v>6300</v>
+        <v>300</v>
       </c>
       <c r="G41" s="3">
-        <v>23700</v>
+        <v>500</v>
       </c>
       <c r="H41" s="3">
-        <v>33700</v>
+        <v>900</v>
       </c>
       <c r="I41" s="3">
-        <v>25400</v>
+        <v>600</v>
       </c>
       <c r="J41" s="3">
-        <v>10200</v>
+        <v>600</v>
       </c>
       <c r="K41" s="3">
         <v>7800</v>
@@ -2228,13 +2228,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2267,25 +2267,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13300</v>
+        <v>2300</v>
       </c>
       <c r="E43" s="3">
-        <v>2200</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
-        <v>4300</v>
+        <v>1500</v>
       </c>
       <c r="G43" s="3">
-        <v>5100</v>
+        <v>1500</v>
       </c>
       <c r="H43" s="3">
-        <v>12600</v>
+        <v>400</v>
       </c>
       <c r="I43" s="3">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="J43" s="3">
-        <v>8600</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>2300</v>
@@ -2318,25 +2318,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8200</v>
+        <v>16200</v>
       </c>
       <c r="E44" s="3">
-        <v>6900</v>
+        <v>2200</v>
       </c>
       <c r="F44" s="3">
-        <v>9300</v>
+        <v>3000</v>
       </c>
       <c r="G44" s="3">
-        <v>13500</v>
+        <v>800</v>
       </c>
       <c r="H44" s="3">
-        <v>10400</v>
+        <v>800</v>
       </c>
       <c r="I44" s="3">
-        <v>10000</v>
+        <v>3400</v>
       </c>
       <c r="J44" s="3">
-        <v>13500</v>
+        <v>2000</v>
       </c>
       <c r="K44" s="3">
         <v>14300</v>
@@ -2369,25 +2369,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>16500</v>
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K45" s="3">
         <v>4400</v>
@@ -2420,25 +2420,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>49300</v>
+        <v>34000</v>
       </c>
       <c r="E46" s="3">
-        <v>16600</v>
+        <v>3400</v>
       </c>
       <c r="F46" s="3">
-        <v>26500</v>
+        <v>5100</v>
       </c>
       <c r="G46" s="3">
-        <v>46100</v>
+        <v>3000</v>
       </c>
       <c r="H46" s="3">
-        <v>58900</v>
+        <v>4000</v>
       </c>
       <c r="I46" s="3">
-        <v>42900</v>
+        <v>5800</v>
       </c>
       <c r="J46" s="3">
-        <v>51000</v>
+        <v>3400</v>
       </c>
       <c r="K46" s="3">
         <v>31400</v>
@@ -2473,14 +2473,14 @@
       <c r="D47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
-        <v>900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>5200</v>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>10</v>
@@ -2522,25 +2522,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>130600</v>
+        <v>35800</v>
       </c>
       <c r="E48" s="3">
-        <v>121600</v>
+        <v>1700</v>
       </c>
       <c r="F48" s="3">
-        <v>132500</v>
+        <v>2600</v>
       </c>
       <c r="G48" s="3">
-        <v>145100</v>
+        <v>10900</v>
       </c>
       <c r="H48" s="3">
-        <v>155700</v>
+        <v>5000</v>
       </c>
       <c r="I48" s="3">
-        <v>61400</v>
+        <v>3400</v>
       </c>
       <c r="J48" s="3">
-        <v>64300</v>
+        <v>5200</v>
       </c>
       <c r="K48" s="3">
         <v>110000</v>
@@ -2726,25 +2726,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="E52" s="3">
-        <v>6800</v>
+        <v>1100</v>
       </c>
       <c r="F52" s="3">
-        <v>6400</v>
+        <v>1700</v>
       </c>
       <c r="G52" s="3">
-        <v>7800</v>
+        <v>1400</v>
       </c>
       <c r="H52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J52" s="3">
         <v>1100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>73900</v>
       </c>
       <c r="K52" s="3">
         <v>1600</v>
@@ -2828,25 +2828,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>184100</v>
+        <v>71700</v>
       </c>
       <c r="E54" s="3">
-        <v>145900</v>
+        <v>6200</v>
       </c>
       <c r="F54" s="3">
-        <v>184000</v>
+        <v>9400</v>
       </c>
       <c r="G54" s="3">
-        <v>210100</v>
+        <v>15400</v>
       </c>
       <c r="H54" s="3">
-        <v>215800</v>
+        <v>10900</v>
       </c>
       <c r="I54" s="3">
-        <v>105700</v>
+        <v>11100</v>
       </c>
       <c r="J54" s="3">
-        <v>193000</v>
+        <v>9700</v>
       </c>
       <c r="K54" s="3">
         <v>150300</v>
@@ -2921,25 +2921,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7400</v>
+        <v>25100</v>
       </c>
       <c r="E57" s="3">
-        <v>11300</v>
+        <v>10600</v>
       </c>
       <c r="F57" s="3">
-        <v>7600</v>
+        <v>13300</v>
       </c>
       <c r="G57" s="3">
-        <v>13300</v>
+        <v>11400</v>
       </c>
       <c r="H57" s="3">
-        <v>13300</v>
+        <v>6400</v>
       </c>
       <c r="I57" s="3">
-        <v>8800</v>
+        <v>6300</v>
       </c>
       <c r="J57" s="3">
-        <v>9100</v>
+        <v>4700</v>
       </c>
       <c r="K57" s="3">
         <v>12400</v>
@@ -2978,19 +2978,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K58" s="3">
         <v>1200</v>
@@ -3023,25 +3023,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>49100</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="F59" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>3400</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>9700</v>
+        <v>300</v>
       </c>
       <c r="I59" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J59" s="3">
-        <v>14900</v>
+        <v>700</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
@@ -3074,25 +3074,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17300</v>
+        <v>74300</v>
       </c>
       <c r="E60" s="3">
-        <v>14500</v>
+        <v>12400</v>
       </c>
       <c r="F60" s="3">
-        <v>11300</v>
+        <v>13500</v>
       </c>
       <c r="G60" s="3">
-        <v>24700</v>
+        <v>15800</v>
       </c>
       <c r="H60" s="3">
-        <v>29700</v>
+        <v>7900</v>
       </c>
       <c r="I60" s="3">
-        <v>12100</v>
+        <v>7400</v>
       </c>
       <c r="J60" s="3">
-        <v>28000</v>
+        <v>6600</v>
       </c>
       <c r="K60" s="3">
         <v>17600</v>
@@ -3131,16 +3131,16 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3176,25 +3176,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>107200</v>
+        <v>12500</v>
       </c>
       <c r="E62" s="3">
-        <v>90100</v>
+        <v>2100</v>
       </c>
       <c r="F62" s="3">
-        <v>77900</v>
+        <v>2100</v>
       </c>
       <c r="G62" s="3">
-        <v>58500</v>
+        <v>2100</v>
       </c>
       <c r="H62" s="3">
-        <v>52200</v>
+        <v>2500</v>
       </c>
       <c r="I62" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="J62" s="3">
-        <v>7000</v>
+        <v>1300</v>
       </c>
       <c r="K62" s="3">
         <v>3300</v>
@@ -3380,25 +3380,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>140000</v>
+        <v>86800</v>
       </c>
       <c r="E66" s="3">
-        <v>118600</v>
+        <v>14600</v>
       </c>
       <c r="F66" s="3">
-        <v>103500</v>
+        <v>15800</v>
       </c>
       <c r="G66" s="3">
-        <v>98300</v>
+        <v>18000</v>
       </c>
       <c r="H66" s="3">
-        <v>95000</v>
+        <v>11100</v>
       </c>
       <c r="I66" s="3">
-        <v>15200</v>
+        <v>10400</v>
       </c>
       <c r="J66" s="3">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="K66" s="3">
         <v>23100</v>
@@ -3656,25 +3656,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-87500</v>
+        <v>-227000</v>
       </c>
       <c r="E72" s="3">
-        <v>-81100</v>
+        <v>-158600</v>
       </c>
       <c r="F72" s="3">
-        <v>-24600</v>
+        <v>-156100</v>
       </c>
       <c r="G72" s="3">
-        <v>7700</v>
+        <v>-149400</v>
       </c>
       <c r="H72" s="3">
-        <v>17600</v>
+        <v>-146300</v>
       </c>
       <c r="I72" s="3">
-        <v>12700</v>
+        <v>-145300</v>
       </c>
       <c r="J72" s="3">
-        <v>16900</v>
+        <v>-144100</v>
       </c>
       <c r="K72" s="3">
         <v>12700</v>
@@ -3860,25 +3860,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>44000</v>
+        <v>-15200</v>
       </c>
       <c r="E76" s="3">
-        <v>27300</v>
+        <v>-8400</v>
       </c>
       <c r="F76" s="3">
-        <v>80400</v>
+        <v>-6400</v>
       </c>
       <c r="G76" s="3">
-        <v>111800</v>
+        <v>-2600</v>
       </c>
       <c r="H76" s="3">
-        <v>120800</v>
+        <v>-200</v>
       </c>
       <c r="I76" s="3">
-        <v>90500</v>
+        <v>700</v>
       </c>
       <c r="J76" s="3">
-        <v>158100</v>
+        <v>1700</v>
       </c>
       <c r="K76" s="3">
         <v>127300</v>
@@ -4018,25 +4018,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6500</v>
+        <v>-68400</v>
       </c>
       <c r="E81" s="3">
-        <v>-56500</v>
+        <v>-2500</v>
       </c>
       <c r="F81" s="3">
-        <v>-24100</v>
+        <v>-6700</v>
       </c>
       <c r="G81" s="3">
-        <v>-6300</v>
+        <v>-3100</v>
       </c>
       <c r="H81" s="3">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="I81" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="J81" s="3">
-        <v>5800</v>
+        <v>-3900</v>
       </c>
       <c r="K81" s="3">
         <v>9300</v>
@@ -4090,25 +4090,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12200</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>19900</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>26100</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>27400</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>16100</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>17600</v>
+        <v>1300</v>
       </c>
       <c r="J83" s="3">
-        <v>19900</v>
+        <v>1400</v>
       </c>
       <c r="K83" s="3">
         <v>15100</v>
@@ -4396,25 +4396,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>21700</v>
+        <v>-12900</v>
       </c>
       <c r="E89" s="3">
-        <v>-600</v>
+        <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>-5200</v>
+        <v>-1900</v>
       </c>
       <c r="G89" s="3">
-        <v>14200</v>
+        <v>-6600</v>
       </c>
       <c r="H89" s="3">
-        <v>34800</v>
+        <v>2200</v>
       </c>
       <c r="I89" s="3">
-        <v>35400</v>
+        <v>-1200</v>
       </c>
       <c r="J89" s="3">
-        <v>21400</v>
+        <v>1800</v>
       </c>
       <c r="K89" s="3">
         <v>22300</v>
@@ -4468,25 +4468,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-21100</v>
+        <v>-4900</v>
       </c>
       <c r="E91" s="3">
-        <v>-7600</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-12500</v>
+        <v>-13800</v>
       </c>
       <c r="G91" s="3">
-        <v>-18200</v>
+        <v>-18300</v>
       </c>
       <c r="H91" s="3">
-        <v>-20600</v>
+        <v>-8000</v>
       </c>
       <c r="I91" s="3">
-        <v>-12800</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-16900</v>
+        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>-24000</v>
@@ -4621,25 +4621,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-20200</v>
+        <v>-10900</v>
       </c>
       <c r="E94" s="3">
-        <v>-6400</v>
+        <v>-200</v>
       </c>
       <c r="F94" s="3">
-        <v>-12500</v>
+        <v>1800</v>
       </c>
       <c r="G94" s="3">
-        <v>-19400</v>
+        <v>3200</v>
       </c>
       <c r="H94" s="3">
-        <v>-23000</v>
+        <v>-1600</v>
       </c>
       <c r="I94" s="3">
-        <v>-14500</v>
+        <v>200</v>
       </c>
       <c r="J94" s="3">
-        <v>-39500</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
         <v>-40100</v>
@@ -4702,16 +4702,16 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>1100</v>
@@ -4897,25 +4897,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>22100</v>
+        <v>33100</v>
       </c>
       <c r="E100" s="3">
-        <v>2700</v>
+        <v>500</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>-3900</v>
+        <v>2900</v>
       </c>
       <c r="H100" s="3">
-        <v>-3100</v>
+        <v>-200</v>
       </c>
       <c r="I100" s="3">
-        <v>-5200</v>
+        <v>1100</v>
       </c>
       <c r="J100" s="3">
-        <v>21000</v>
+        <v>-1400</v>
       </c>
       <c r="K100" s="3">
         <v>3500</v>
@@ -4947,26 +4947,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-500</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K101" s="3">
         <v>-300</v>
@@ -4999,25 +4999,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>23400</v>
+        <v>9200</v>
       </c>
       <c r="E102" s="3">
-        <v>-4600</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
-        <v>-17400</v>
+        <v>-200</v>
       </c>
       <c r="G102" s="3">
-        <v>-10000</v>
+        <v>-500</v>
       </c>
       <c r="H102" s="3">
-        <v>8300</v>
+        <v>400</v>
       </c>
       <c r="I102" s="3">
-        <v>15200</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="K102" s="3">
         <v>-14600</v>
